--- a/sepsis_project - Students Version/recovered_69pct/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/recovered_69pct/ddqn_ppo_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,22 +448,67 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Mean Return Std</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Survival Rate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Rate Std</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Length</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Length Std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Training Episodes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Eval Seeds</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Eval Episodes / Seed</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Best Trial</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Best Checkpoint Episode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Checkpoint Survival</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Checkpoint Return</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>buffer_size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>target_update_freq</t>
         </is>
       </c>
     </row>
@@ -474,20 +519,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5603718</v>
+        <v>0.56219023</v>
       </c>
       <c r="C2" t="n">
-        <v>0.65312</v>
+        <v>0.00245445981546857</v>
       </c>
       <c r="D2" t="n">
+        <v>0.654656</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.002438581554920796</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -500,19 +582,44 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6357</v>
+        <v>0.5762179599999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.00234919543391987</v>
       </c>
       <c r="D3" t="n">
+        <v>0.66348</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00234064093786295</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.409644</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02628140559406987</v>
+      </c>
+      <c r="H3" t="n">
         <v>50000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6105725</v>
+      </c>
+      <c r="O3" t="n">
         <v>100000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -522,20 +629,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6314</v>
+        <v>0.6560038500000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.674</v>
+        <v>0.002557427440808439</v>
       </c>
       <c r="D4" t="n">
+        <v>0.6774919999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.002534821492728833</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.376943999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.02381606768549321</v>
+      </c>
+      <c r="H4" t="n">
         <v>50000</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/A (on-policy)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>46000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6915074999999999</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>N/A (on-policy)</t>
         </is>
@@ -2374,13 +2504,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5766199999999999</v>
+        <v>0.65385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.63</v>
+        <v>0.674</v>
       </c>
       <c r="D2" t="n">
-        <v>8.646000000000001</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="3">
@@ -2388,13 +2518,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6330800000000001</v>
+        <v>0.6585250000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="D3" t="n">
-        <v>8.792</v>
+        <v>6.906</v>
       </c>
     </row>
     <row r="4">
@@ -2402,13 +2532,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6427550000000001</v>
+        <v>0.6162450000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>0.698</v>
+        <v>0.638</v>
       </c>
       <c r="D4" t="n">
-        <v>8.882</v>
+        <v>7.524</v>
       </c>
     </row>
     <row r="5">
@@ -2416,13 +2546,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6637550000000001</v>
+        <v>0.6747150000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>0.716</v>
+        <v>0.696</v>
       </c>
       <c r="D5" t="n">
-        <v>8.678000000000001</v>
+        <v>7.238</v>
       </c>
     </row>
     <row r="6">
@@ -2430,13 +2560,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.640835</v>
+        <v>0.6614650000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>7.808</v>
+        <v>7.23</v>
       </c>
     </row>
   </sheetData>
@@ -2480,13 +2610,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.630565</v>
+        <v>0.605565</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.628</v>
       </c>
       <c r="D2" t="n">
-        <v>8.412000000000001</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="3">
@@ -2494,13 +2624,13 @@
         <v>0.05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.649245</v>
+        <v>0.622405</v>
       </c>
       <c r="C3" t="n">
-        <v>0.702</v>
+        <v>0.644</v>
       </c>
       <c r="D3" t="n">
-        <v>8.676</v>
+        <v>7.446</v>
       </c>
     </row>
     <row r="4">
@@ -2508,13 +2638,13 @@
         <v>0.15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6427550000000001</v>
+        <v>0.6162450000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>0.698</v>
+        <v>0.638</v>
       </c>
       <c r="D4" t="n">
-        <v>8.882</v>
+        <v>7.524</v>
       </c>
     </row>
     <row r="5">
@@ -2522,13 +2652,13 @@
         <v>0.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5855750000000001</v>
+        <v>0.6695650000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>8.757999999999999</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="6">
@@ -2536,13 +2666,13 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.619325</v>
+        <v>0.6742950000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.674</v>
+        <v>0.694</v>
       </c>
       <c r="D6" t="n">
-        <v>8.512</v>
+        <v>6.894</v>
       </c>
     </row>
   </sheetData>
@@ -2586,13 +2716,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6751200000000001</v>
+        <v>0.6866350000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.73</v>
+        <v>0.708</v>
       </c>
       <c r="D2" t="n">
-        <v>8.692</v>
+        <v>7.622</v>
       </c>
     </row>
     <row r="3">
@@ -2600,13 +2730,13 @@
         <v>0.005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.642845</v>
+        <v>0.6506199999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.672</v>
       </c>
       <c r="D3" t="n">
-        <v>8.622</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="4">
@@ -2614,13 +2744,13 @@
         <v>0.01</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6427550000000001</v>
+        <v>0.6162450000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>0.698</v>
+        <v>0.638</v>
       </c>
       <c r="D4" t="n">
-        <v>8.882</v>
+        <v>7.524</v>
       </c>
     </row>
     <row r="5">
@@ -2628,13 +2758,13 @@
         <v>0.02</v>
       </c>
       <c r="B5" t="n">
-        <v>0.586635</v>
+        <v>0.61837</v>
       </c>
       <c r="C5" t="n">
-        <v>0.636</v>
+        <v>0.638</v>
       </c>
       <c r="D5" t="n">
-        <v>8.416</v>
+        <v>6.716</v>
       </c>
     </row>
     <row r="6">
@@ -2642,13 +2772,13 @@
         <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.50745</v>
+        <v>0.509765</v>
       </c>
       <c r="C6" t="n">
-        <v>0.544</v>
+        <v>0.528</v>
       </c>
       <c r="D6" t="n">
-        <v>6.064</v>
+        <v>6.068</v>
       </c>
     </row>
   </sheetData>

--- a/sepsis_project - Students Version/recovered_69pct/ddqn_ppo_results.xlsx
+++ b/sepsis_project - Students Version/recovered_69pct/ddqn_ppo_results.xlsx
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.56219023</v>
+        <v>0.5606557799999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00245445981546857</v>
+        <v>0.001085376124668317</v>
       </c>
       <c r="D2" t="n">
-        <v>0.654656</v>
+        <v>0.6532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002438581554920796</v>
+        <v>0.0008709764635166401</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
